--- a/exports/workshop-images/workshop-images-for-wordpress-all-workshops-with-pictures.xlsx
+++ b/exports/workshop-images/workshop-images-for-wordpress-all-workshops-with-pictures.xlsx
@@ -217,6 +217,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -242,6 +245,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -272,6 +278,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -297,6 +306,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -322,6 +334,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -352,6 +367,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -377,6 +395,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -402,6 +423,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -427,6 +451,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -452,6 +479,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -477,6 +507,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -502,6 +535,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -527,6 +563,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -552,6 +591,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -577,6 +619,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -602,6 +647,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -627,6 +675,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -652,6 +703,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -677,6 +731,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -702,6 +759,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -727,6 +787,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -752,6 +815,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -777,6 +843,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -802,6 +871,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -827,6 +899,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -852,6 +927,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -877,6 +955,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -902,6 +983,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -927,6 +1011,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -952,6 +1039,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -977,6 +1067,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1002,6 +1095,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1027,6 +1123,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1052,6 +1151,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1077,6 +1179,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1102,6 +1207,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1127,6 +1235,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1152,6 +1263,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1177,6 +1291,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1202,6 +1319,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1232,6 +1352,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1257,6 +1380,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1282,6 +1408,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1307,6 +1436,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1337,6 +1469,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1362,6 +1497,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1387,6 +1525,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1412,6 +1553,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1437,6 +1581,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1462,6 +1609,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1487,6 +1637,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1512,6 +1665,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1537,6 +1693,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1562,6 +1721,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1587,6 +1749,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1612,6 +1777,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1637,6 +1805,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1662,6 +1833,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1687,6 +1861,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1712,6 +1889,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1737,6 +1917,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1762,6 +1945,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1787,6 +1973,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1812,6 +2001,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1837,6 +2029,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1862,6 +2057,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1887,6 +2085,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1912,6 +2113,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1937,6 +2141,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1967,6 +2174,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1992,6 +2202,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2022,6 +2235,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2047,6 +2263,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2077,6 +2296,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2102,6 +2324,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2127,6 +2352,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2152,6 +2380,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2177,6 +2408,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2207,6 +2441,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2232,6 +2469,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2257,6 +2497,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2287,6 +2530,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2312,6 +2558,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2337,6 +2586,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2362,6 +2614,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2387,6 +2642,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2412,6 +2670,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2437,6 +2698,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2448,6 +2712,81 @@
       <row>11</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="2476500" cy="1390650"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>12</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2476500" cy="1390650"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2476500" cy="1390650"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1619250" cy="904875"/>
     <pic>
       <nvPicPr>
@@ -2455,22 +2794,50 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>12</row>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2476500" cy="1390650"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>16</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1619250" cy="904875"/>
@@ -2480,22 +2847,25 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>13</row>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>17</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1333500" cy="1000125"/>
@@ -2505,22 +2875,75 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>14</row>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId14"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2476500" cy="1390650"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId15"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2476500" cy="1390650"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="16" name="Image 16" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId16"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>20</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="552450" cy="1000125"/>
@@ -2530,22 +2953,25 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>15</row>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId17"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>21</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1333500" cy="1000125"/>
@@ -2555,22 +2981,50 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>16</row>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId18"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>22</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2476500" cy="1390650"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="19" name="Image 19" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId19"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>23</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1619250" cy="904875"/>
@@ -2580,22 +3034,25 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>17</row>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId20"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>24</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="819150" cy="1000125"/>
@@ -2605,22 +3062,25 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId14"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>18</row>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId21"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>25</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1619250" cy="904875"/>
@@ -2630,22 +3090,25 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId15"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>19</row>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId22"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>26</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1333500" cy="1000125"/>
@@ -2655,22 +3118,25 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId16"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>20</row>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId23"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>27</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1333500" cy="1000125"/>
@@ -2680,22 +3146,25 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId17"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>21</row>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId24"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>28</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1619250" cy="904875"/>
@@ -2705,22 +3174,125 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId18"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>22</row>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId25"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>29</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2476500" cy="1390650"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="26" name="Image 26" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId26"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>30</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2476500" cy="1390650"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="27" name="Image 27" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId27"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>31</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2476500" cy="1390650"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="28" name="Image 28" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId28"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>32</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2476500" cy="1390650"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="29" name="Image 29" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId29"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>33</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="742950" cy="1000125"/>
@@ -2730,22 +3302,25 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId19"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>23</row>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId30"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>34</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1333500" cy="1000125"/>
@@ -2755,22 +3330,75 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId20"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>24</row>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId31"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>35</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2476500" cy="1390650"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="32" name="Image 32" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId32"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>36</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2476500" cy="1390650"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="33" name="Image 33" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId33"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>37</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="742950" cy="1000125"/>
@@ -2780,22 +3408,25 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId21"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>25</row>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId34"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>38</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="742950" cy="1000125"/>
@@ -2805,22 +3436,75 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId22"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>26</row>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId35"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2476500" cy="1390650"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="36" name="Image 36" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId36"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>40</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2476500" cy="1390650"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="37" name="Image 37" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId37"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>41</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="742950" cy="1000125"/>
@@ -2830,22 +3514,25 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId23"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>27</row>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId38"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>42</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1333500" cy="1000125"/>
@@ -2855,22 +3542,25 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId24"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>28</row>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId39"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>43</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1619250" cy="904875"/>
@@ -2880,22 +3570,25 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId25"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>29</row>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId40"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>44</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="742950" cy="1000125"/>
@@ -2905,22 +3598,150 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId26"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>30</row>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId41"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2476500" cy="1390650"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="42" name="Image 42" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId42"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>46</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2476500" cy="1390650"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="43" name="Image 43" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId43"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>47</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2476500" cy="1390650"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="44" name="Image 44" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId44"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>48</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2476500" cy="1390650"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="45" name="Image 45" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId45"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>49</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2476500" cy="1390650"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="46" name="Image 46" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId46"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>50</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1619250" cy="904875"/>
@@ -2930,22 +3751,25 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId27"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>31</row>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId47"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>51</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1619250" cy="904875"/>
@@ -2955,13 +3779,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId28"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId48"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2992,6 +3819,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3017,6 +3847,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3042,6 +3875,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3067,6 +3903,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3092,6 +3931,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3117,6 +3959,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3142,6 +3987,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3167,6 +4015,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3192,6 +4043,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3217,6 +4071,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3242,6 +4099,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3267,6 +4127,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3292,6 +4155,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3317,6 +4183,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3342,6 +4211,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3367,6 +4239,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3392,6 +4267,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3417,6 +4295,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3442,6 +4323,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3467,6 +4351,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3492,6 +4379,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3517,6 +4407,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3542,6 +4435,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3567,6 +4463,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3592,6 +4491,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3617,6 +4519,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3642,6 +4547,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3667,6 +4575,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3697,6 +4608,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3722,6 +4636,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3747,6 +4664,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3772,6 +4692,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3797,6 +4720,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3822,6 +4748,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3847,6 +4776,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3872,6 +4804,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3897,6 +4832,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3922,6 +4860,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3947,6 +4888,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3972,6 +4916,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3997,6 +4944,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4022,6 +4972,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4047,6 +5000,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4072,6 +5028,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4097,6 +5056,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4122,6 +5084,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4147,6 +5112,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4172,6 +5140,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4197,6 +5168,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4222,6 +5196,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4247,6 +5224,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4272,6 +5252,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4297,6 +5280,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4322,6 +5308,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4347,6 +5336,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4372,6 +5364,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4397,6 +5392,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4422,6 +5420,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4452,6 +5453,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4477,6 +5481,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4502,6 +5509,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4527,6 +5537,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4552,6 +5565,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4577,6 +5593,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4602,6 +5621,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4627,6 +5649,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4652,6 +5677,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4677,6 +5705,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4702,6 +5733,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4727,6 +5761,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4752,6 +5789,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4777,6 +5817,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4802,6 +5845,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4827,6 +5873,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4852,6 +5901,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4877,6 +5929,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4902,6 +5957,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4927,6 +5985,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4952,6 +6013,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4977,6 +6041,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5002,6 +6069,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5027,6 +6097,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5052,6 +6125,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5077,6 +6153,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5102,6 +6181,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5127,6 +6209,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5152,6 +6237,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5177,6 +6265,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5202,6 +6293,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5227,6 +6321,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5252,6 +6349,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5769,7 +6869,7 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>1</v>
@@ -5781,7 +6881,7 @@
         <v>4</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="H10" s="2" t="inlineStr"/>
     </row>
@@ -5981,6 +7081,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
@@ -6029,7 +7130,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -7483,7 +8583,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -7697,7 +8796,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -9259,7 +10357,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -9523,7 +10620,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -10649,7 +11745,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -10833,7 +11928,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -11017,7 +12111,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -11201,7 +12294,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -11491,7 +12583,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -11675,7 +12766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:K52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -11705,7 +12796,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -12007,7 +13097,7 @@
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>Photo 1 of 22, under the heading "Photos from the workshop"</t>
+          <t>Photo 1 of 42, under the heading "Photos from the workshop"</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
@@ -12030,8 +13120,8 @@
           <t>Synergia Ranch, our home for the two weeks</t>
         </is>
       </c>
-      <c r="J11" s="8" t="inlineStr"/>
-      <c r="K11" s="8" t="inlineStr"/>
+      <c r="J11" s="8" t="n"/>
+      <c r="K11" s="8" t="n"/>
     </row>
     <row r="12" ht="79.25" customHeight="1">
       <c r="A12" s="8" t="n">
@@ -12039,7 +13129,7 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>accelerator-workshop-february-2026-gallery-02-baby-goat.jpg</t>
+          <t>accelerator-workshop-february-2026-gallery-02-cholla.jpg</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
@@ -12049,7 +13139,7 @@
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>Photo 2 of 22, under the heading "Photos from the workshop"</t>
+          <t>Photo 2 of 42, under the heading "Photos from the workshop"</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
@@ -12059,21 +13149,25 @@
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>1600 x 900</t>
+          <t>1600 x 901</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>A baby goat lying in dry grass next to a sheep</t>
+          <t>Cholla cactus with small yellow fruit in dry grass, hills and blue sky behind</t>
         </is>
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>A new friend at the ranch</t>
-        </is>
-      </c>
-      <c r="J12" s="8" t="inlineStr"/>
-      <c r="K12" s="8" t="inlineStr"/>
+          <t>Cholla cactus on the ranch</t>
+        </is>
+      </c>
+      <c r="J12" s="8" t="n"/>
+      <c r="K12" s="8" t="inlineStr">
+        <is>
+          <t>Added 14 Oct 2026 (Photos-Feb26-CTPAW)</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="79.25" customHeight="1">
       <c r="A13" s="8" t="n">
@@ -12081,7 +13175,7 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>accelerator-workshop-february-2026-gallery-03-classroom.jpg</t>
+          <t>accelerator-workshop-february-2026-gallery-03-windrow-in-the-desert.jpg</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
@@ -12091,7 +13185,7 @@
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>Photo 3 of 22, under the heading "Photos from the workshop"</t>
+          <t>Photo 3 of 42, under the heading "Photos from the workshop"</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr">
@@ -12101,29 +13195,33 @@
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>1600 x 900</t>
+          <t>1600 x 901</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>A full classroom seen from the back: long tables, a wooden beam ceiling and many students with laptops</t>
+          <t>A long compost windrow on dry ground, bare trees, juniper and blue mountains behind</t>
         </is>
       </c>
       <c r="I13" s="8" t="inlineStr">
         <is>
-          <t>A full classroom</t>
-        </is>
-      </c>
-      <c r="J13" s="8" t="inlineStr"/>
-      <c r="K13" s="8" t="inlineStr"/>
-    </row>
-    <row r="14" ht="86.75" customHeight="1">
+          <t>A windrow in the high desert</t>
+        </is>
+      </c>
+      <c r="J13" s="8" t="n"/>
+      <c r="K13" s="8" t="inlineStr">
+        <is>
+          <t>Added 14 Oct 2026 (Photos-Feb26-CTPAW)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="79.25" customHeight="1">
       <c r="A14" s="8" t="n">
         <v>10</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>accelerator-workshop-february-2026-gallery-04-instructor-at-whiteboard.jpg</t>
+          <t>accelerator-workshop-february-2026-gallery-04-wagon-wheels.jpg</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
@@ -12133,7 +13231,7 @@
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>Photo 4 of 22, under the heading "Photos from the workshop"</t>
+          <t>Photo 4 of 42, under the heading "Photos from the workshop"</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
@@ -12143,29 +13241,33 @@
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>1600 x 1200</t>
+          <t>1600 x 901</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>An instructor in a plaid shirt speaking into a microphone in front of a whiteboard</t>
+          <t>Old wooden wagon wheels lying in dry grass under bare trees</t>
         </is>
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>Class in session</t>
-        </is>
-      </c>
-      <c r="J14" s="8" t="inlineStr"/>
-      <c r="K14" s="8" t="inlineStr"/>
-    </row>
-    <row r="15" ht="86.75" customHeight="1">
+          <t>Old wagon wheels in the scrub</t>
+        </is>
+      </c>
+      <c r="J14" s="8" t="n"/>
+      <c r="K14" s="8" t="inlineStr">
+        <is>
+          <t>Added 14 Oct 2026 (Photos-Feb26-CTPAW)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="79.25" customHeight="1">
       <c r="A15" s="8" t="n">
         <v>11</v>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>accelerator-workshop-february-2026-gallery-05-instructor-outdoors.jpg</t>
+          <t>accelerator-workshop-february-2026-gallery-05-baby-goat.jpg</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
@@ -12175,7 +13277,7 @@
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>Photo 5 of 22, under the heading "Photos from the workshop"</t>
+          <t>Photo 5 of 42, under the heading "Photos from the workshop"</t>
         </is>
       </c>
       <c r="F15" s="8" t="inlineStr">
@@ -12185,29 +13287,29 @@
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>900 x 1600</t>
+          <t>1600 x 900</t>
         </is>
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>An instructor in a rust fleece speaking outdoors, with a shed and a hoop house behind him</t>
+          <t>A baby goat lying in dry grass next to a sheep</t>
         </is>
       </c>
       <c r="I15" s="8" t="inlineStr">
         <is>
-          <t>Teaching outdoors</t>
-        </is>
-      </c>
-      <c r="J15" s="8" t="inlineStr"/>
-      <c r="K15" s="8" t="inlineStr"/>
-    </row>
-    <row r="16" ht="86.75" customHeight="1">
+          <t>A new friend at the ranch</t>
+        </is>
+      </c>
+      <c r="J15" s="8" t="n"/>
+      <c r="K15" s="8" t="n"/>
+    </row>
+    <row r="16" ht="79.25" customHeight="1">
       <c r="A16" s="8" t="n">
         <v>12</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>accelerator-workshop-february-2026-gallery-06-class-walking.jpg</t>
+          <t>accelerator-workshop-february-2026-gallery-06-flower-tiles.jpg</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
@@ -12217,7 +13319,7 @@
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>Photo 6 of 22, under the heading "Photos from the workshop"</t>
+          <t>Photo 6 of 42, under the heading "Photos from the workshop"</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
@@ -12227,21 +13329,25 @@
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>1600 x 1200</t>
+          <t>1600 x 901</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>The class walking in a line along a dirt path through dry scrub</t>
+          <t>Wall tiles painted with yellow flowers between rows of green tiles</t>
         </is>
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>Off on a walk across the ranch</t>
-        </is>
-      </c>
-      <c r="J16" s="8" t="inlineStr"/>
-      <c r="K16" s="8" t="inlineStr"/>
+          <t>Yellow flower tiles</t>
+        </is>
+      </c>
+      <c r="J16" s="8" t="n"/>
+      <c r="K16" s="8" t="inlineStr">
+        <is>
+          <t>Added 14 Oct 2026 (Photos-Feb26-CTPAW)</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="79.25" customHeight="1">
       <c r="A17" s="8" t="n">
@@ -12249,7 +13355,7 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>accelerator-workshop-february-2026-gallery-07-inspecting-feedstock.jpg</t>
+          <t>accelerator-workshop-february-2026-gallery-07-classroom.jpg</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
@@ -12259,7 +13365,7 @@
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>Photo 7 of 22, under the heading "Photos from the workshop"</t>
+          <t>Photo 7 of 42, under the heading "Photos from the workshop"</t>
         </is>
       </c>
       <c r="F17" s="8" t="inlineStr">
@@ -12274,16 +13380,16 @@
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>A woman in a red jacket reaching into a blue drum of dry feedstock, with students in green caps around her</t>
+          <t>A full classroom seen from the back: long tables, a wooden beam ceiling and many students with laptops</t>
         </is>
       </c>
       <c r="I17" s="8" t="inlineStr">
         <is>
-          <t>Getting hands-on with feedstock</t>
-        </is>
-      </c>
-      <c r="J17" s="8" t="inlineStr"/>
-      <c r="K17" s="8" t="inlineStr"/>
+          <t>A full classroom</t>
+        </is>
+      </c>
+      <c r="J17" s="8" t="n"/>
+      <c r="K17" s="8" t="n"/>
     </row>
     <row r="18" ht="86.75" customHeight="1">
       <c r="A18" s="8" t="n">
@@ -12291,7 +13397,7 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>accelerator-workshop-february-2026-gallery-08-students-at-feedstock-drums.jpg</t>
+          <t>accelerator-workshop-february-2026-gallery-08-instructor-at-whiteboard.jpg</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
@@ -12301,7 +13407,7 @@
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>Photo 8 of 22, under the heading "Photos from the workshop"</t>
+          <t>Photo 8 of 42, under the heading "Photos from the workshop"</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
@@ -12311,21 +13417,21 @@
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>900 x 1100</t>
+          <t>1600 x 1200</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>Students crouched and kneeling at blue drums of feedstock, with shade structures behind</t>
+          <t>An instructor in a plaid shirt speaking into a microphone in front of a whiteboard</t>
         </is>
       </c>
       <c r="I18" s="8" t="inlineStr">
         <is>
-          <t>Inspecting feedstock together</t>
-        </is>
-      </c>
-      <c r="J18" s="8" t="inlineStr"/>
-      <c r="K18" s="8" t="inlineStr"/>
+          <t>Class in session</t>
+        </is>
+      </c>
+      <c r="J18" s="8" t="n"/>
+      <c r="K18" s="8" t="n"/>
     </row>
     <row r="19" ht="79.25" customHeight="1">
       <c r="A19" s="8" t="n">
@@ -12333,7 +13439,7 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>accelerator-workshop-february-2026-gallery-09-feedstock-from-above.jpg</t>
+          <t>accelerator-workshop-february-2026-gallery-09-comparing-notes.jpg</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
@@ -12343,7 +13449,7 @@
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>Photo 9 of 22, under the heading "Photos from the workshop"</t>
+          <t>Photo 9 of 42, under the heading "Photos from the workshop"</t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr">
@@ -12353,29 +13459,33 @@
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>1600 x 900</t>
+          <t>1600 x 901</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>Blue drums of dry stems seen from above, a hand reaching in and a person in a straw hat</t>
+          <t>A bearded man in a green cap and a woman looking at something in his hands in the classroom, students at laptops behind</t>
         </is>
       </c>
       <c r="I19" s="8" t="inlineStr">
         <is>
-          <t>Feedstock, up close</t>
-        </is>
-      </c>
-      <c r="J19" s="8" t="inlineStr"/>
-      <c r="K19" s="8" t="inlineStr"/>
-    </row>
-    <row r="20" ht="86.75" customHeight="1">
+          <t>Comparing notes in the classroom</t>
+        </is>
+      </c>
+      <c r="J19" s="8" t="n"/>
+      <c r="K19" s="8" t="inlineStr">
+        <is>
+          <t>Added 14 Oct 2026 (Photos-Feb26-CTPAW)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="79.25" customHeight="1">
       <c r="A20" s="8" t="n">
         <v>16</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>accelerator-workshop-february-2026-gallery-10-aged-wood-chips.jpg</t>
+          <t>accelerator-workshop-february-2026-gallery-10-sample-to-the-light.jpg</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
@@ -12385,7 +13495,7 @@
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>Photo 10 of 22, under the heading "Photos from the workshop"</t>
+          <t>Photo 10 of 42, under the heading "Photos from the workshop"</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr">
@@ -12395,21 +13505,25 @@
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>1600 x 1200</t>
+          <t>1600 x 901</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>A pile of aged wood chips with a blue label reading "Aged wood chips"</t>
+          <t>A woman in a plaid shirt and name tag holding up a pipette and a sample tube in the classroom, a projector screen behind</t>
         </is>
       </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
-          <t>Aged wood chips, ready for the pile</t>
-        </is>
-      </c>
-      <c r="J20" s="8" t="inlineStr"/>
-      <c r="K20" s="8" t="inlineStr"/>
+          <t>A sample, held up to the light</t>
+        </is>
+      </c>
+      <c r="J20" s="8" t="n"/>
+      <c r="K20" s="8" t="inlineStr">
+        <is>
+          <t>Added 14 Oct 2026 (Photos-Feb26-CTPAW)</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="86.75" customHeight="1">
       <c r="A21" s="8" t="n">
@@ -12417,7 +13531,7 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>accelerator-workshop-february-2026-gallery-11-alfalfa-cubes.jpg</t>
+          <t>accelerator-workshop-february-2026-gallery-11-instructor-outdoors.jpg</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
@@ -12427,7 +13541,7 @@
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>Photo 11 of 22, under the heading "Photos from the workshop"</t>
+          <t>Photo 11 of 42, under the heading "Photos from the workshop"</t>
         </is>
       </c>
       <c r="F21" s="8" t="inlineStr">
@@ -12437,29 +13551,29 @@
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>1600 x 1200</t>
+          <t>900 x 1600</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>A sack labeled "Alfalfa Cubes, net wt. 50 lb"</t>
+          <t>An instructor in a rust fleece speaking outdoors, with a shed and a hoop house behind him</t>
         </is>
       </c>
       <c r="I21" s="8" t="inlineStr">
         <is>
-          <t>Alfalfa cubes for the compost recipe</t>
-        </is>
-      </c>
-      <c r="J21" s="8" t="inlineStr"/>
-      <c r="K21" s="8" t="inlineStr"/>
-    </row>
-    <row r="22" ht="79.25" customHeight="1">
+          <t>Teaching outdoors</t>
+        </is>
+      </c>
+      <c r="J21" s="8" t="n"/>
+      <c r="K21" s="8" t="n"/>
+    </row>
+    <row r="22" ht="86.75" customHeight="1">
       <c r="A22" s="8" t="n">
         <v>18</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>accelerator-workshop-february-2026-gallery-12-feedstock-buckets.jpg</t>
+          <t>accelerator-workshop-february-2026-gallery-12-class-walking.jpg</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
@@ -12469,7 +13583,7 @@
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>Photo 12 of 22, under the heading "Photos from the workshop"</t>
+          <t>Photo 12 of 42, under the heading "Photos from the workshop"</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
@@ -12479,29 +13593,29 @@
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>1600 x 900</t>
+          <t>1600 x 1200</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>Rows of blue buckets of dark feedstock, with a hoop house and a hill behind</t>
+          <t>The class walking in a line along a dirt path through dry scrub</t>
         </is>
       </c>
       <c r="I22" s="8" t="inlineStr">
         <is>
-          <t>Feedstocks lined up for pile building</t>
-        </is>
-      </c>
-      <c r="J22" s="8" t="inlineStr"/>
-      <c r="K22" s="8" t="inlineStr"/>
-    </row>
-    <row r="23" ht="86.75" customHeight="1">
+          <t>Off on a walk across the ranch</t>
+        </is>
+      </c>
+      <c r="J22" s="8" t="n"/>
+      <c r="K22" s="8" t="n"/>
+    </row>
+    <row r="23" ht="79.25" customHeight="1">
       <c r="A23" s="8" t="n">
         <v>19</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>accelerator-workshop-february-2026-gallery-13-thermometer-in-hay-bale.jpg</t>
+          <t>accelerator-workshop-february-2026-gallery-13-by-the-hoop-houses.jpg</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
@@ -12511,7 +13625,7 @@
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>Photo 13 of 22, under the heading "Photos from the workshop"</t>
+          <t>Photo 13 of 42, under the heading "Photos from the workshop"</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr">
@@ -12521,29 +13635,33 @@
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
-          <t>1200 x 1600</t>
+          <t>1600 x 901</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>A long-stem compost thermometer and a sun hat on a hay bale</t>
+          <t>Three men smiling in front of a row of shade-cloth hoop houses, a blue tarp and pallets beside them, clear blue sky</t>
         </is>
       </c>
       <c r="I23" s="8" t="inlineStr">
         <is>
-          <t>The compost thermometer, always close at hand</t>
-        </is>
-      </c>
-      <c r="J23" s="8" t="inlineStr"/>
-      <c r="K23" s="8" t="inlineStr"/>
-    </row>
-    <row r="24" ht="86.75" customHeight="1">
+          <t>By the hoop houses</t>
+        </is>
+      </c>
+      <c r="J23" s="8" t="n"/>
+      <c r="K23" s="8" t="inlineStr">
+        <is>
+          <t>Added 14 Oct 2026 (Photos-Feb26-CTPAW)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="79.25" customHeight="1">
       <c r="A24" s="8" t="n">
         <v>20</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>accelerator-workshop-february-2026-gallery-14-class-in-hoop-house.jpg</t>
+          <t>accelerator-workshop-february-2026-gallery-14-inspecting-feedstock.jpg</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
@@ -12553,7 +13671,7 @@
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>Photo 14 of 22, under the heading "Photos from the workshop"</t>
+          <t>Photo 14 of 42, under the heading "Photos from the workshop"</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
@@ -12563,21 +13681,21 @@
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>1600 x 1200</t>
+          <t>1600 x 900</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>Students in caps and wide hats standing close together inside a hoop house, listening</t>
+          <t>A woman in a red jacket reaching into a blue drum of dry feedstock, with students in green caps around her</t>
         </is>
       </c>
       <c r="I24" s="8" t="inlineStr">
         <is>
-          <t>Listening in the hoop house</t>
-        </is>
-      </c>
-      <c r="J24" s="8" t="inlineStr"/>
-      <c r="K24" s="8" t="inlineStr"/>
+          <t>Getting hands-on with feedstock</t>
+        </is>
+      </c>
+      <c r="J24" s="8" t="n"/>
+      <c r="K24" s="8" t="n"/>
     </row>
     <row r="25" ht="86.75" customHeight="1">
       <c r="A25" s="8" t="n">
@@ -12585,7 +13703,7 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>accelerator-workshop-february-2026-gallery-15-insulated-compost-pile.jpg</t>
+          <t>accelerator-workshop-february-2026-gallery-15-students-at-feedstock-drums.jpg</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
@@ -12595,7 +13713,7 @@
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>Photo 15 of 22, under the heading "Photos from the workshop"</t>
+          <t>Photo 15 of 42, under the heading "Photos from the workshop"</t>
         </is>
       </c>
       <c r="F25" s="8" t="inlineStr">
@@ -12605,29 +13723,29 @@
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>1200 x 1600</t>
+          <t>900 x 1100</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>A woody compost pile in a hoop house, its base wrapped in reflective insulation</t>
+          <t>Students crouched and kneeling at blue drums of feedstock, with shade structures behind</t>
         </is>
       </c>
       <c r="I25" s="8" t="inlineStr">
         <is>
-          <t>A pile wrapped up against the winter cold</t>
-        </is>
-      </c>
-      <c r="J25" s="8" t="inlineStr"/>
-      <c r="K25" s="8" t="inlineStr"/>
-    </row>
-    <row r="26" ht="86.75" customHeight="1">
+          <t>Inspecting feedstock together</t>
+        </is>
+      </c>
+      <c r="J25" s="8" t="n"/>
+      <c r="K25" s="8" t="n"/>
+    </row>
+    <row r="26" ht="79.25" customHeight="1">
       <c r="A26" s="8" t="n">
         <v>22</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>accelerator-workshop-february-2026-gallery-16-compost-row-in-hoop-house.jpg</t>
+          <t>accelerator-workshop-february-2026-gallery-16-feedstock-from-above.jpg</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
@@ -12637,7 +13755,7 @@
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>Photo 16 of 22, under the heading "Photos from the workshop"</t>
+          <t>Photo 16 of 42, under the heading "Photos from the workshop"</t>
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr">
@@ -12647,21 +13765,21 @@
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>1200 x 1600</t>
+          <t>1600 x 900</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>The inside of a hoop house with a long row of dark compost</t>
+          <t>Blue drums of dry stems seen from above, a hand reaching in and a person in a straw hat</t>
         </is>
       </c>
       <c r="I26" s="8" t="inlineStr">
         <is>
-          <t>A long row of compost in the hoop house</t>
-        </is>
-      </c>
-      <c r="J26" s="8" t="inlineStr"/>
-      <c r="K26" s="8" t="inlineStr"/>
+          <t>Feedstock, up close</t>
+        </is>
+      </c>
+      <c r="J26" s="8" t="n"/>
+      <c r="K26" s="8" t="n"/>
     </row>
     <row r="27" ht="86.75" customHeight="1">
       <c r="A27" s="8" t="n">
@@ -12669,7 +13787,7 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>accelerator-workshop-february-2026-gallery-17-worm-bin.jpg</t>
+          <t>accelerator-workshop-february-2026-gallery-17-aged-wood-chips.jpg</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
@@ -12679,7 +13797,7 @@
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>Photo 17 of 22, under the heading "Photos from the workshop"</t>
+          <t>Photo 17 of 42, under the heading "Photos from the workshop"</t>
         </is>
       </c>
       <c r="F27" s="8" t="inlineStr">
@@ -12689,21 +13807,21 @@
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>1200 x 1600</t>
+          <t>1600 x 1200</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>A wooden worm bin full of vermicompost under hanging lights</t>
+          <t>A pile of aged wood chips with a blue label reading "Aged wood chips"</t>
         </is>
       </c>
       <c r="I27" s="8" t="inlineStr">
         <is>
-          <t>The worm bin</t>
-        </is>
-      </c>
-      <c r="J27" s="8" t="inlineStr"/>
-      <c r="K27" s="8" t="inlineStr"/>
+          <t>Aged wood chips, ready for the pile</t>
+        </is>
+      </c>
+      <c r="J27" s="8" t="n"/>
+      <c r="K27" s="8" t="n"/>
     </row>
     <row r="28" ht="86.75" customHeight="1">
       <c r="A28" s="8" t="n">
@@ -12711,7 +13829,7 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>accelerator-workshop-february-2026-gallery-18-microscopy-lab.jpg</t>
+          <t>accelerator-workshop-february-2026-gallery-18-alfalfa-cubes.jpg</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
@@ -12721,7 +13839,7 @@
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>Photo 18 of 22, under the heading "Photos from the workshop"</t>
+          <t>Photo 18 of 42, under the heading "Photos from the workshop"</t>
         </is>
       </c>
       <c r="F28" s="8" t="inlineStr">
@@ -12736,16 +13854,16 @@
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>A microscopy lab: students at white microscopes and laptops while mentors point things out</t>
+          <t>A sack labeled "Alfalfa Cubes, net wt. 50 lb"</t>
         </is>
       </c>
       <c r="I28" s="8" t="inlineStr">
         <is>
-          <t>The microscopy lab in full swing</t>
-        </is>
-      </c>
-      <c r="J28" s="8" t="inlineStr"/>
-      <c r="K28" s="8" t="inlineStr"/>
+          <t>Alfalfa cubes for the compost recipe</t>
+        </is>
+      </c>
+      <c r="J28" s="8" t="n"/>
+      <c r="K28" s="8" t="n"/>
     </row>
     <row r="29" ht="79.25" customHeight="1">
       <c r="A29" s="8" t="n">
@@ -12753,7 +13871,7 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>accelerator-workshop-february-2026-gallery-19-at-the-microscope.jpg</t>
+          <t>accelerator-workshop-february-2026-gallery-19-feedstock-buckets.jpg</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
@@ -12763,7 +13881,7 @@
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>Photo 19 of 22, under the heading "Photos from the workshop"</t>
+          <t>Photo 19 of 42, under the heading "Photos from the workshop"</t>
         </is>
       </c>
       <c r="F29" s="8" t="inlineStr">
@@ -12778,24 +13896,24 @@
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>A woman looking into a microscope, with a mentor in a plaid shirt behind her</t>
+          <t>Rows of blue buckets of dark feedstock, with a hoop house and a hill behind</t>
         </is>
       </c>
       <c r="I29" s="8" t="inlineStr">
         <is>
-          <t>Looking closely, with a mentor nearby</t>
-        </is>
-      </c>
-      <c r="J29" s="8" t="inlineStr"/>
-      <c r="K29" s="8" t="inlineStr"/>
-    </row>
-    <row r="30" ht="86.75" customHeight="1">
+          <t>Feedstocks lined up for pile building</t>
+        </is>
+      </c>
+      <c r="J29" s="8" t="n"/>
+      <c r="K29" s="8" t="n"/>
+    </row>
+    <row r="30" ht="79.25" customHeight="1">
       <c r="A30" s="8" t="n">
         <v>26</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>accelerator-workshop-february-2026-gallery-20-mentor-with-microscopes.jpg</t>
+          <t>accelerator-workshop-february-2026-gallery-20-lifting-a-drum.jpg</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
@@ -12805,7 +13923,7 @@
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>Photo 20 of 22, under the heading "Photos from the workshop"</t>
+          <t>Photo 20 of 42, under the heading "Photos from the workshop"</t>
         </is>
       </c>
       <c r="F30" s="8" t="inlineStr">
@@ -12815,21 +13933,25 @@
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>1200 x 1600</t>
+          <t>1600 x 901</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>A white-bearded mentor smiling beside a row of microscopes</t>
+          <t>A man in a straw cowboy hat lifting a blue drum over a heap of feedstock beside a hoop house</t>
         </is>
       </c>
       <c r="I30" s="8" t="inlineStr">
         <is>
-          <t>One of our mentors, all smiles at the microscopes</t>
-        </is>
-      </c>
-      <c r="J30" s="8" t="inlineStr"/>
-      <c r="K30" s="8" t="inlineStr"/>
+          <t>Moving feedstock by the drum</t>
+        </is>
+      </c>
+      <c r="J30" s="8" t="n"/>
+      <c r="K30" s="8" t="inlineStr">
+        <is>
+          <t>Added 14 Oct 2026 (Photos-Feb26-CTPAW)</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="79.25" customHeight="1">
       <c r="A31" s="8" t="n">
@@ -12837,7 +13959,7 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>accelerator-workshop-february-2026-gallery-21-caps.jpg</t>
+          <t>accelerator-workshop-february-2026-gallery-21-carrying-a-drum.jpg</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
@@ -12847,7 +13969,7 @@
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>Photo 21 of 22, under the heading "Photos from the workshop"</t>
+          <t>Photo 21 of 42, under the heading "Photos from the workshop"</t>
         </is>
       </c>
       <c r="F31" s="8" t="inlineStr">
@@ -12857,21 +13979,25 @@
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>1600 x 900</t>
+          <t>1600 x 901</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>Dark green Soil Food Web caps on a table</t>
+          <t>A young man in a cap carrying a blue drum inside a hoop house, students and a pile of feedstock around him</t>
         </is>
       </c>
       <c r="I31" s="8" t="inlineStr">
         <is>
-          <t>Workshop caps, ready to wear</t>
-        </is>
-      </c>
-      <c r="J31" s="8" t="inlineStr"/>
-      <c r="K31" s="8" t="inlineStr"/>
+          <t>Hauling drums in the hoop house</t>
+        </is>
+      </c>
+      <c r="J31" s="8" t="n"/>
+      <c r="K31" s="8" t="inlineStr">
+        <is>
+          <t>Added 14 Oct 2026 (Photos-Feb26-CTPAW)</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="79.25" customHeight="1">
       <c r="A32" s="8" t="n">
@@ -12879,7 +14005,7 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>accelerator-workshop-february-2026-gallery-22-certificate.jpg</t>
+          <t>accelerator-workshop-february-2026-gallery-22-everyone-in-close.jpg</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
@@ -12889,7 +14015,7 @@
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>Photo 22 of 22, under the heading "Photos from the workshop"</t>
+          <t>Photo 22 of 42, under the heading "Photos from the workshop"</t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
@@ -12899,21 +14025,905 @@
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
+          <t>1600 x 901</t>
+        </is>
+      </c>
+      <c r="H32" s="8" t="inlineStr">
+        <is>
+          <t>The class crowded and crouching around blue buckets on the ground, seen from above</t>
+        </is>
+      </c>
+      <c r="I32" s="8" t="inlineStr">
+        <is>
+          <t>Everyone in close</t>
+        </is>
+      </c>
+      <c r="J32" s="8" t="n"/>
+      <c r="K32" s="8" t="inlineStr">
+        <is>
+          <t>Added 14 Oct 2026 (Photos-Feb26-CTPAW)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="79.25" customHeight="1">
+      <c r="A33" s="8" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>accelerator-workshop-february-2026-gallery-23-tiny-find.jpg</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>Gallery (bottom of page)</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>Photo 23 of 42, under the heading "Photos from the workshop"</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>Justified grid of whole photos; click opens the full photo with its caption</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t>1600 x 901</t>
+        </is>
+      </c>
+      <c r="H33" s="8" t="inlineStr">
+        <is>
+          <t>An open palm with a tiny dark organism on it, close-up</t>
+        </is>
+      </c>
+      <c r="I33" s="8" t="inlineStr">
+        <is>
+          <t>A tiny find in the palm of a hand</t>
+        </is>
+      </c>
+      <c r="J33" s="8" t="n"/>
+      <c r="K33" s="8" t="inlineStr">
+        <is>
+          <t>Added 14 Oct 2026 (Photos-Feb26-CTPAW)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="86.75" customHeight="1">
+      <c r="A34" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>accelerator-workshop-february-2026-gallery-24-thermometer-in-hay-bale.jpg</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>Gallery (bottom of page)</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>Photo 24 of 42, under the heading "Photos from the workshop"</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="inlineStr">
+        <is>
+          <t>Justified grid of whole photos; click opens the full photo with its caption</t>
+        </is>
+      </c>
+      <c r="G34" s="8" t="inlineStr">
+        <is>
+          <t>1200 x 1600</t>
+        </is>
+      </c>
+      <c r="H34" s="8" t="inlineStr">
+        <is>
+          <t>A long-stem compost thermometer and a sun hat on a hay bale</t>
+        </is>
+      </c>
+      <c r="I34" s="8" t="inlineStr">
+        <is>
+          <t>The compost thermometer, always close at hand</t>
+        </is>
+      </c>
+      <c r="J34" s="8" t="n"/>
+      <c r="K34" s="8" t="n"/>
+    </row>
+    <row r="35" ht="86.75" customHeight="1">
+      <c r="A35" s="8" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>accelerator-workshop-february-2026-gallery-25-class-in-hoop-house.jpg</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>Gallery (bottom of page)</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>Photo 25 of 42, under the heading "Photos from the workshop"</t>
+        </is>
+      </c>
+      <c r="F35" s="8" t="inlineStr">
+        <is>
+          <t>Justified grid of whole photos; click opens the full photo with its caption</t>
+        </is>
+      </c>
+      <c r="G35" s="8" t="inlineStr">
+        <is>
+          <t>1600 x 1200</t>
+        </is>
+      </c>
+      <c r="H35" s="8" t="inlineStr">
+        <is>
+          <t>Students in caps and wide hats standing close together inside a hoop house, listening</t>
+        </is>
+      </c>
+      <c r="I35" s="8" t="inlineStr">
+        <is>
+          <t>Listening in the hoop house</t>
+        </is>
+      </c>
+      <c r="J35" s="8" t="n"/>
+      <c r="K35" s="8" t="n"/>
+    </row>
+    <row r="36" ht="79.25" customHeight="1">
+      <c r="A36" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>accelerator-workshop-february-2026-gallery-26-tossing-hay.jpg</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>Gallery (bottom of page)</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>Photo 26 of 42, under the heading "Photos from the workshop"</t>
+        </is>
+      </c>
+      <c r="F36" s="8" t="inlineStr">
+        <is>
+          <t>Justified grid of whole photos; click opens the full photo with its caption</t>
+        </is>
+      </c>
+      <c r="G36" s="8" t="inlineStr">
+        <is>
+          <t>1600 x 901</t>
+        </is>
+      </c>
+      <c r="H36" s="8" t="inlineStr">
+        <is>
+          <t>A man tossing hay onto a pile inside a hoop house, dust in the air</t>
+        </is>
+      </c>
+      <c r="I36" s="8" t="inlineStr">
+        <is>
+          <t>Building a pile in the hoop house</t>
+        </is>
+      </c>
+      <c r="J36" s="8" t="n"/>
+      <c r="K36" s="8" t="inlineStr">
+        <is>
+          <t>Added 14 Oct 2026 (Photos-Feb26-CTPAW)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="79.25" customHeight="1">
+      <c r="A37" s="8" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>accelerator-workshop-february-2026-gallery-27-lifting-the-cage.jpg</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>Gallery (bottom of page)</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>Photo 27 of 42, under the heading "Photos from the workshop"</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>Justified grid of whole photos; click opens the full photo with its caption</t>
+        </is>
+      </c>
+      <c r="G37" s="8" t="inlineStr">
+        <is>
+          <t>1600 x 901</t>
+        </is>
+      </c>
+      <c r="H37" s="8" t="inlineStr">
+        <is>
+          <t>Two people lifting a wire cage off a compost pile inside a hoop house, a hay bale in front</t>
+        </is>
+      </c>
+      <c r="I37" s="8" t="inlineStr">
+        <is>
+          <t>Lifting the cage off a pile</t>
+        </is>
+      </c>
+      <c r="J37" s="8" t="n"/>
+      <c r="K37" s="8" t="inlineStr">
+        <is>
+          <t>Added 14 Oct 2026 (Photos-Feb26-CTPAW)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="86.75" customHeight="1">
+      <c r="A38" s="8" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>accelerator-workshop-february-2026-gallery-28-insulated-compost-pile.jpg</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>Gallery (bottom of page)</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t>Photo 28 of 42, under the heading "Photos from the workshop"</t>
+        </is>
+      </c>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t>Justified grid of whole photos; click opens the full photo with its caption</t>
+        </is>
+      </c>
+      <c r="G38" s="8" t="inlineStr">
+        <is>
+          <t>1200 x 1600</t>
+        </is>
+      </c>
+      <c r="H38" s="8" t="inlineStr">
+        <is>
+          <t>A woody compost pile in a hoop house, its base wrapped in reflective insulation</t>
+        </is>
+      </c>
+      <c r="I38" s="8" t="inlineStr">
+        <is>
+          <t>A pile wrapped up against the winter cold</t>
+        </is>
+      </c>
+      <c r="J38" s="8" t="n"/>
+      <c r="K38" s="8" t="n"/>
+    </row>
+    <row r="39" ht="86.75" customHeight="1">
+      <c r="A39" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>accelerator-workshop-february-2026-gallery-29-compost-row-in-hoop-house.jpg</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>Gallery (bottom of page)</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t>Photo 29 of 42, under the heading "Photos from the workshop"</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t>Justified grid of whole photos; click opens the full photo with its caption</t>
+        </is>
+      </c>
+      <c r="G39" s="8" t="inlineStr">
+        <is>
+          <t>1200 x 1600</t>
+        </is>
+      </c>
+      <c r="H39" s="8" t="inlineStr">
+        <is>
+          <t>The inside of a hoop house with a long row of dark compost</t>
+        </is>
+      </c>
+      <c r="I39" s="8" t="inlineStr">
+        <is>
+          <t>A long row of compost in the hoop house</t>
+        </is>
+      </c>
+      <c r="J39" s="8" t="n"/>
+      <c r="K39" s="8" t="n"/>
+    </row>
+    <row r="40" ht="79.25" customHeight="1">
+      <c r="A40" s="8" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>accelerator-workshop-february-2026-gallery-30-checking-the-bin.jpg</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>Gallery (bottom of page)</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t>Photo 30 of 42, under the heading "Photos from the workshop"</t>
+        </is>
+      </c>
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t>Justified grid of whole photos; click opens the full photo with its caption</t>
+        </is>
+      </c>
+      <c r="G40" s="8" t="inlineStr">
+        <is>
+          <t>1600 x 901</t>
+        </is>
+      </c>
+      <c r="H40" s="8" t="inlineStr">
+        <is>
+          <t>A woman in sunglasses kneeling at a wire compost bin and reaching into the pile, a blue bucket beside her</t>
+        </is>
+      </c>
+      <c r="I40" s="8" t="inlineStr">
+        <is>
+          <t>Checking inside the bin</t>
+        </is>
+      </c>
+      <c r="J40" s="8" t="n"/>
+      <c r="K40" s="8" t="inlineStr">
+        <is>
+          <t>Added 14 Oct 2026 (Photos-Feb26-CTPAW)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="79.25" customHeight="1">
+      <c r="A41" s="8" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>accelerator-workshop-february-2026-gallery-31-smiles-at-the-bin.jpg</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>Gallery (bottom of page)</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t>Photo 31 of 42, under the heading "Photos from the workshop"</t>
+        </is>
+      </c>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>Justified grid of whole photos; click opens the full photo with its caption</t>
+        </is>
+      </c>
+      <c r="G41" s="8" t="inlineStr">
+        <is>
+          <t>1600 x 901</t>
+        </is>
+      </c>
+      <c r="H41" s="8" t="inlineStr">
+        <is>
+          <t>A smiling woman in a purple hoodie and pink gloves leaning over a round wire bin, a man in a cap behind her</t>
+        </is>
+      </c>
+      <c r="I41" s="8" t="inlineStr">
+        <is>
+          <t>All smiles at the compost bin</t>
+        </is>
+      </c>
+      <c r="J41" s="8" t="n"/>
+      <c r="K41" s="8" t="inlineStr">
+        <is>
+          <t>Added 14 Oct 2026 (Photos-Feb26-CTPAW)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="86.75" customHeight="1">
+      <c r="A42" s="8" t="n">
+        <v>38</v>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>accelerator-workshop-february-2026-gallery-32-worm-bin.jpg</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>Gallery (bottom of page)</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t>Photo 32 of 42, under the heading "Photos from the workshop"</t>
+        </is>
+      </c>
+      <c r="F42" s="8" t="inlineStr">
+        <is>
+          <t>Justified grid of whole photos; click opens the full photo with its caption</t>
+        </is>
+      </c>
+      <c r="G42" s="8" t="inlineStr">
+        <is>
+          <t>1200 x 1600</t>
+        </is>
+      </c>
+      <c r="H42" s="8" t="inlineStr">
+        <is>
+          <t>A wooden worm bin full of vermicompost under hanging lights</t>
+        </is>
+      </c>
+      <c r="I42" s="8" t="inlineStr">
+        <is>
+          <t>The worm bin</t>
+        </is>
+      </c>
+      <c r="J42" s="8" t="n"/>
+      <c r="K42" s="8" t="n"/>
+    </row>
+    <row r="43" ht="86.75" customHeight="1">
+      <c r="A43" s="8" t="n">
+        <v>39</v>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>accelerator-workshop-february-2026-gallery-33-microscopy-lab.jpg</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>Gallery (bottom of page)</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t>Photo 33 of 42, under the heading "Photos from the workshop"</t>
+        </is>
+      </c>
+      <c r="F43" s="8" t="inlineStr">
+        <is>
+          <t>Justified grid of whole photos; click opens the full photo with its caption</t>
+        </is>
+      </c>
+      <c r="G43" s="8" t="inlineStr">
+        <is>
+          <t>1600 x 1200</t>
+        </is>
+      </c>
+      <c r="H43" s="8" t="inlineStr">
+        <is>
+          <t>A microscopy lab: students at white microscopes and laptops while mentors point things out</t>
+        </is>
+      </c>
+      <c r="I43" s="8" t="inlineStr">
+        <is>
+          <t>The microscopy lab in full swing</t>
+        </is>
+      </c>
+      <c r="J43" s="8" t="n"/>
+      <c r="K43" s="8" t="n"/>
+    </row>
+    <row r="44" ht="79.25" customHeight="1">
+      <c r="A44" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>accelerator-workshop-february-2026-gallery-34-at-the-microscope.jpg</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>Gallery (bottom of page)</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t>Photo 34 of 42, under the heading "Photos from the workshop"</t>
+        </is>
+      </c>
+      <c r="F44" s="8" t="inlineStr">
+        <is>
+          <t>Justified grid of whole photos; click opens the full photo with its caption</t>
+        </is>
+      </c>
+      <c r="G44" s="8" t="inlineStr">
+        <is>
           <t>1600 x 900</t>
         </is>
       </c>
-      <c r="H32" s="8" t="inlineStr">
+      <c r="H44" s="8" t="inlineStr">
+        <is>
+          <t>A woman looking into a microscope, with a mentor in a plaid shirt behind her</t>
+        </is>
+      </c>
+      <c r="I44" s="8" t="inlineStr">
+        <is>
+          <t>Looking closely, with a mentor nearby</t>
+        </is>
+      </c>
+      <c r="J44" s="8" t="n"/>
+      <c r="K44" s="8" t="n"/>
+    </row>
+    <row r="45" ht="86.75" customHeight="1">
+      <c r="A45" s="8" t="n">
+        <v>41</v>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>accelerator-workshop-february-2026-gallery-35-mentor-with-microscopes.jpg</t>
+        </is>
+      </c>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>Gallery (bottom of page)</t>
+        </is>
+      </c>
+      <c r="E45" s="8" t="inlineStr">
+        <is>
+          <t>Photo 35 of 42, under the heading "Photos from the workshop"</t>
+        </is>
+      </c>
+      <c r="F45" s="8" t="inlineStr">
+        <is>
+          <t>Justified grid of whole photos; click opens the full photo with its caption</t>
+        </is>
+      </c>
+      <c r="G45" s="8" t="inlineStr">
+        <is>
+          <t>1200 x 1600</t>
+        </is>
+      </c>
+      <c r="H45" s="8" t="inlineStr">
+        <is>
+          <t>A white-bearded mentor smiling beside a row of microscopes</t>
+        </is>
+      </c>
+      <c r="I45" s="8" t="inlineStr">
+        <is>
+          <t>One of our mentors, all smiles at the microscopes</t>
+        </is>
+      </c>
+      <c r="J45" s="8" t="n"/>
+      <c r="K45" s="8" t="n"/>
+    </row>
+    <row r="46" ht="79.25" customHeight="1">
+      <c r="A46" s="8" t="n">
+        <v>42</v>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>accelerator-workshop-february-2026-gallery-36-extraction-stands.jpg</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t>Gallery (bottom of page)</t>
+        </is>
+      </c>
+      <c r="E46" s="8" t="inlineStr">
+        <is>
+          <t>Photo 36 of 42, under the heading "Photos from the workshop"</t>
+        </is>
+      </c>
+      <c r="F46" s="8" t="inlineStr">
+        <is>
+          <t>Justified grid of whole photos; click opens the full photo with its caption</t>
+        </is>
+      </c>
+      <c r="G46" s="8" t="inlineStr">
+        <is>
+          <t>1600 x 901</t>
+        </is>
+      </c>
+      <c r="H46" s="8" t="inlineStr">
+        <is>
+          <t>A man in a green shirt lifting a blue bucket beside white funnel stands with yellow tubing, students watching</t>
+        </is>
+      </c>
+      <c r="I46" s="8" t="inlineStr">
+        <is>
+          <t>At the extraction stands</t>
+        </is>
+      </c>
+      <c r="J46" s="8" t="n"/>
+      <c r="K46" s="8" t="inlineStr">
+        <is>
+          <t>Added 14 Oct 2026 (Photos-Feb26-CTPAW)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="79.25" customHeight="1">
+      <c r="A47" s="8" t="n">
+        <v>43</v>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>accelerator-workshop-february-2026-gallery-37-carts-by-the-dome.jpg</t>
+        </is>
+      </c>
+      <c r="D47" s="8" t="inlineStr">
+        <is>
+          <t>Gallery (bottom of page)</t>
+        </is>
+      </c>
+      <c r="E47" s="8" t="inlineStr">
+        <is>
+          <t>Photo 37 of 42, under the heading "Photos from the workshop"</t>
+        </is>
+      </c>
+      <c r="F47" s="8" t="inlineStr">
+        <is>
+          <t>Justified grid of whole photos; click opens the full photo with its caption</t>
+        </is>
+      </c>
+      <c r="G47" s="8" t="inlineStr">
+        <is>
+          <t>1600 x 901</t>
+        </is>
+      </c>
+      <c r="H47" s="8" t="inlineStr">
+        <is>
+          <t>Students at rows of metal carts with equipment outdoors, a geodesic dome and bare trees behind</t>
+        </is>
+      </c>
+      <c r="I47" s="8" t="inlineStr">
+        <is>
+          <t>Working outdoors by the dome</t>
+        </is>
+      </c>
+      <c r="J47" s="8" t="n"/>
+      <c r="K47" s="8" t="inlineStr">
+        <is>
+          <t>Added 14 Oct 2026 (Photos-Feb26-CTPAW)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="79.25" customHeight="1">
+      <c r="A48" s="8" t="n">
+        <v>44</v>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>accelerator-workshop-february-2026-gallery-38-dinner-together.jpg</t>
+        </is>
+      </c>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t>Gallery (bottom of page)</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t>Photo 38 of 42, under the heading "Photos from the workshop"</t>
+        </is>
+      </c>
+      <c r="F48" s="8" t="inlineStr">
+        <is>
+          <t>Justified grid of whole photos; click opens the full photo with its caption</t>
+        </is>
+      </c>
+      <c r="G48" s="8" t="inlineStr">
+        <is>
+          <t>1600 x 901</t>
+        </is>
+      </c>
+      <c r="H48" s="8" t="inlineStr">
+        <is>
+          <t>The class around a long dinner table with plates of food, in a white room with paintings</t>
+        </is>
+      </c>
+      <c r="I48" s="8" t="inlineStr">
+        <is>
+          <t>Dinner together</t>
+        </is>
+      </c>
+      <c r="J48" s="8" t="n"/>
+      <c r="K48" s="8" t="inlineStr">
+        <is>
+          <t>Added 14 Oct 2026 (Photos-Feb26-CTPAW)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="79.25" customHeight="1">
+      <c r="A49" s="8" t="n">
+        <v>45</v>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>accelerator-workshop-february-2026-gallery-39-birthday-candles.jpg</t>
+        </is>
+      </c>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>Gallery (bottom of page)</t>
+        </is>
+      </c>
+      <c r="E49" s="8" t="inlineStr">
+        <is>
+          <t>Photo 39 of 42, under the heading "Photos from the workshop"</t>
+        </is>
+      </c>
+      <c r="F49" s="8" t="inlineStr">
+        <is>
+          <t>Justified grid of whole photos; click opens the full photo with its caption</t>
+        </is>
+      </c>
+      <c r="G49" s="8" t="inlineStr">
+        <is>
+          <t>1600 x 901</t>
+        </is>
+      </c>
+      <c r="H49" s="8" t="inlineStr">
+        <is>
+          <t>A woman blowing out the candles on a chocolate birthday cake, a man standing beside her</t>
+        </is>
+      </c>
+      <c r="I49" s="8" t="inlineStr">
+        <is>
+          <t>Birthday candles</t>
+        </is>
+      </c>
+      <c r="J49" s="8" t="n"/>
+      <c r="K49" s="8" t="inlineStr">
+        <is>
+          <t>Added 14 Oct 2026 (Photos-Feb26-CTPAW)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="79.25" customHeight="1">
+      <c r="A50" s="8" t="n">
+        <v>46</v>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>accelerator-workshop-february-2026-gallery-40-sunset-over-the-mountains.jpg</t>
+        </is>
+      </c>
+      <c r="D50" s="8" t="inlineStr">
+        <is>
+          <t>Gallery (bottom of page)</t>
+        </is>
+      </c>
+      <c r="E50" s="8" t="inlineStr">
+        <is>
+          <t>Photo 40 of 42, under the heading "Photos from the workshop"</t>
+        </is>
+      </c>
+      <c r="F50" s="8" t="inlineStr">
+        <is>
+          <t>Justified grid of whole photos; click opens the full photo with its caption</t>
+        </is>
+      </c>
+      <c r="G50" s="8" t="inlineStr">
+        <is>
+          <t>1600 x 901</t>
+        </is>
+      </c>
+      <c r="H50" s="8" t="inlineStr">
+        <is>
+          <t>Orange clouds over dark mountain silhouettes at sunset, scrub in the foreground</t>
+        </is>
+      </c>
+      <c r="I50" s="8" t="inlineStr">
+        <is>
+          <t>Sunset over the mountains</t>
+        </is>
+      </c>
+      <c r="J50" s="8" t="n"/>
+      <c r="K50" s="8" t="inlineStr">
+        <is>
+          <t>Added 14 Oct 2026 (Photos-Feb26-CTPAW)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="79.25" customHeight="1">
+      <c r="A51" s="8" t="n">
+        <v>47</v>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>accelerator-workshop-february-2026-gallery-41-caps.jpg</t>
+        </is>
+      </c>
+      <c r="D51" s="8" t="inlineStr">
+        <is>
+          <t>Gallery (bottom of page)</t>
+        </is>
+      </c>
+      <c r="E51" s="8" t="inlineStr">
+        <is>
+          <t>Photo 41 of 42, under the heading "Photos from the workshop"</t>
+        </is>
+      </c>
+      <c r="F51" s="8" t="inlineStr">
+        <is>
+          <t>Justified grid of whole photos; click opens the full photo with its caption</t>
+        </is>
+      </c>
+      <c r="G51" s="8" t="inlineStr">
+        <is>
+          <t>1600 x 900</t>
+        </is>
+      </c>
+      <c r="H51" s="8" t="inlineStr">
+        <is>
+          <t>Dark green Soil Food Web caps on a table</t>
+        </is>
+      </c>
+      <c r="I51" s="8" t="inlineStr">
+        <is>
+          <t>Workshop caps, ready to wear</t>
+        </is>
+      </c>
+      <c r="J51" s="8" t="n"/>
+      <c r="K51" s="8" t="n"/>
+    </row>
+    <row r="52" ht="79.25" customHeight="1">
+      <c r="A52" s="8" t="n">
+        <v>48</v>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>accelerator-workshop-february-2026-gallery-42-certificate.jpg</t>
+        </is>
+      </c>
+      <c r="D52" s="8" t="inlineStr">
+        <is>
+          <t>Gallery (bottom of page)</t>
+        </is>
+      </c>
+      <c r="E52" s="8" t="inlineStr">
+        <is>
+          <t>Photo 42 of 42, under the heading "Photos from the workshop"</t>
+        </is>
+      </c>
+      <c r="F52" s="8" t="inlineStr">
+        <is>
+          <t>Justified grid of whole photos; click opens the full photo with its caption</t>
+        </is>
+      </c>
+      <c r="G52" s="8" t="inlineStr">
+        <is>
+          <t>1600 x 900</t>
+        </is>
+      </c>
+      <c r="H52" s="8" t="inlineStr">
         <is>
           <t>Two people in an adobe room, one holding a graduation certificate</t>
         </is>
       </c>
-      <c r="I32" s="8" t="inlineStr">
+      <c r="I52" s="8" t="inlineStr">
         <is>
           <t>A proud graduate</t>
         </is>
       </c>
-      <c r="J32" s="8" t="inlineStr"/>
-      <c r="K32" s="8" t="inlineStr"/>
+      <c r="J52" s="8" t="n"/>
+      <c r="K52" s="8" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12957,7 +14967,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -14221,7 +16230,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
